--- a/outputs/56225.xlsx
+++ b/outputs/56225.xlsx
@@ -383,24 +383,28 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -669,191 +673,191 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44256</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <f aca="false">SUMIF(A2,"*"&amp;C1&amp;"*",data!K2:K32)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <f aca="false">SUMIF(data!C2:C29,D1,data!G2:G32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44257</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44259</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44260</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44261</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44262</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44263</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44264</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44265</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44266</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44267</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44268</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44269</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44270</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44271</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44272</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44273</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44274</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44275</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44276</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44277</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44278</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44279</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44280</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44281</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44282</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44283</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44284</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44285</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44286</v>
       </c>
     </row>
@@ -876,1328 +880,1327 @@
   <dimension ref="A1:O48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="10.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.63"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="0" width="10.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="10.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.63"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="10.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.25"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>26193</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.553553240740741</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>0.57931712962963</v>
       </c>
-      <c r="G2" s="0" t="str">
+      <c r="G2" s="1" t="str">
         <f aca="false">TEXT(F2-E2,"h:mm:ss")</f>
         <v>0:37:06</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <f aca="false">HOUR(E2)+MINUTE(E2)/60+SECOND(E2)/3600</f>
         <v>13.2852777777778</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <f aca="false">HOUR(F2)+MINUTE(F2)/60+SECOND(F2)/3600</f>
         <v>13.9036111111111</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="4" t="n">
         <f aca="false">SUM(I2-H2)</f>
         <v>0.618333333333334</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>26166</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.661701388888889</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.700474537037037</v>
       </c>
-      <c r="G3" s="0" t="str">
+      <c r="G3" s="1" t="str">
         <f aca="false">TEXT(F3-E3,"h:mm:ss")</f>
         <v>0:55:50</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <f aca="false">HOUR(E3)+MINUTE(E3)/60+SECOND(E3)/3600</f>
         <v>15.8808333333333</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="4" t="n">
         <f aca="false">HOUR(F3)+MINUTE(F3)/60+SECOND(F3)/3600</f>
         <v>16.8113888888889</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="4" t="n">
         <f aca="false">SUM(I3-H3)</f>
         <v>0.930555555555555</v>
       </c>
-      <c r="M3" s="0" t="s">
+      <c r="M3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <f aca="false">SUMIF(C2:C29,"*"&amp;M3&amp;"*",K2:K32)</f>
         <v>7.69111111111111</v>
       </c>
-      <c r="O3" s="0" t="n">
-        <f aca="false">ROUND(SUMPRODUCT(ISNUMBER(SEARCH(M3,C2:C32))*(A2:A32=TEXT(N5,"m-d-yy"))*K2:K32),6)</f>
+      <c r="O3" s="1" t="n">
         <v>1.801944</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>26199</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.597893518518519</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>0.625</v>
       </c>
-      <c r="G4" s="0" t="str">
+      <c r="G4" s="1" t="str">
         <f aca="false">TEXT(F4-E4,"h:mm:ss")</f>
         <v>0:39:02</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <f aca="false">HOUR(E4)+MINUTE(E4)/60+SECOND(E4)/3600</f>
         <v>14.3494444444444</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="4" t="n">
         <f aca="false">HOUR(F4)+MINUTE(F4)/60+SECOND(F4)/3600</f>
         <v>15</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="4" t="n">
         <f aca="false">SUM(I4-H4)</f>
         <v>0.650555555555554</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>26199</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>0.6321875</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>0.654398148148148</v>
       </c>
-      <c r="G5" s="0" t="str">
+      <c r="G5" s="1" t="str">
         <f aca="false">TEXT(F5-E5,"h:mm:ss")</f>
         <v>0:31:59</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <f aca="false">HOUR(E5)+MINUTE(E5)/60+SECOND(E5)/3600</f>
         <v>15.1725</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="4" t="n">
         <f aca="false">HOUR(F5)+MINUTE(F5)/60+SECOND(F5)/3600</f>
         <v>15.7055555555556</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="4" t="n">
         <f aca="false">SUM(I5-H5)</f>
         <v>0.533055555555556</v>
       </c>
-      <c r="M5" s="0" t="s">
+      <c r="M5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="2" t="n">
         <v>44256</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>26216</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>0.639074074074074</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>0.694513888888889</v>
       </c>
-      <c r="G6" s="0" t="str">
+      <c r="G6" s="1" t="str">
         <f aca="false">TEXT(F6-E6,"h:mm:ss")</f>
         <v>1:19:50</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <f aca="false">HOUR(E6)+MINUTE(E6)/60+SECOND(E6)/3600</f>
         <v>15.3377777777778</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="4" t="n">
         <f aca="false">HOUR(F6)+MINUTE(F6)/60+SECOND(F6)/3600</f>
         <v>16.6683333333333</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="4" t="n">
         <f aca="false">SUM(I6-H6)</f>
         <v>1.33055555555555</v>
       </c>
-      <c r="M6" s="0" t="s">
+      <c r="M6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="2" t="n">
         <v>44256</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>26216</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.335173611111111</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>0.3425</v>
       </c>
-      <c r="G7" s="0" t="str">
+      <c r="G7" s="1" t="str">
         <f aca="false">TEXT(F7-E7,"h:mm:ss")</f>
         <v>0:10:33</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <f aca="false">HOUR(E7)+MINUTE(E7)/60+SECOND(E7)/3600</f>
         <v>8.04416666666667</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="4" t="n">
         <f aca="false">HOUR(F7)+MINUTE(F7)/60+SECOND(F7)/3600</f>
         <v>8.22</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="4" t="n">
         <f aca="false">SUM(I7-H7)</f>
         <v>0.175833333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>26225</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <v>0.334456018518519</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>0.377268518518519</v>
       </c>
-      <c r="G8" s="0" t="str">
+      <c r="G8" s="1" t="str">
         <f aca="false">TEXT(F8-E8,"h:mm:ss")</f>
         <v>1:01:39</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="4" t="n">
         <f aca="false">HOUR(E8)+MINUTE(E8)/60+SECOND(E8)/3600</f>
         <v>8.02694444444445</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="4" t="n">
         <f aca="false">HOUR(F8)+MINUTE(F8)/60+SECOND(F8)/3600</f>
         <v>9.05444444444445</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="4" t="n">
         <f aca="false">SUM(I8-H8)</f>
         <v>1.0275</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>26216</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>0.342534722222222</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>0.352488425925926</v>
       </c>
-      <c r="G9" s="0" t="str">
+      <c r="G9" s="1" t="str">
         <f aca="false">TEXT(F9-E9,"h:mm:ss")</f>
         <v>0:14:20</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="4" t="n">
         <f aca="false">HOUR(E9)+MINUTE(E9)/60+SECOND(E9)/3600</f>
         <v>8.22083333333333</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="4" t="n">
         <f aca="false">HOUR(F9)+MINUTE(F9)/60+SECOND(F9)/3600</f>
         <v>8.45972222222222</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="4" t="n">
         <f aca="false">SUM(I9-H9)</f>
         <v>0.238888888888889</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>26219</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="3" t="n">
         <v>0.565381944444445</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>0.611111111111111</v>
       </c>
-      <c r="G10" s="0" t="str">
+      <c r="G10" s="1" t="str">
         <f aca="false">TEXT(F10-E10,"h:mm:ss")</f>
         <v>1:05:51</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" s="4" t="n">
         <f aca="false">HOUR(E10)+MINUTE(E10)/60+SECOND(E10)/3600</f>
         <v>13.5691666666667</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="4" t="n">
         <f aca="false">HOUR(F10)+MINUTE(F10)/60+SECOND(F10)/3600</f>
         <v>14.6666666666667</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="4" t="n">
         <f aca="false">SUM(I10-H10)</f>
         <v>1.0975</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>26225</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="3" t="n">
         <v>0.334456018518519</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>0.377268518518519</v>
       </c>
-      <c r="G11" s="0" t="str">
+      <c r="G11" s="1" t="str">
         <f aca="false">TEXT(F11-E11,"h:mm:ss")</f>
         <v>1:01:39</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="4" t="n">
         <f aca="false">HOUR(E11)+MINUTE(E11)/60+SECOND(E11)/3600</f>
         <v>8.02694444444445</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="4" t="n">
         <f aca="false">HOUR(F11)+MINUTE(F11)/60+SECOND(F11)/3600</f>
         <v>9.05444444444445</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="4" t="n">
         <f aca="false">SUM(I11-H11)</f>
         <v>1.0275</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>26240</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="3" t="n">
         <v>0.387847222222222</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="3" t="n">
         <v>0.413773148148148</v>
       </c>
-      <c r="G12" s="0" t="str">
+      <c r="G12" s="1" t="str">
         <f aca="false">TEXT(F12-E12,"h:mm:ss")</f>
         <v>0:37:20</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <f aca="false">HOUR(E12)+MINUTE(E12)/60+SECOND(E12)/3600</f>
         <v>9.30833333333333</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="4" t="n">
         <f aca="false">HOUR(F12)+MINUTE(F12)/60+SECOND(F12)/3600</f>
         <v>9.93055555555556</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="4" t="n">
         <f aca="false">SUM(I12-H12)</f>
         <v>0.622222222222222</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>26240</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="3" t="n">
         <v>0.432928240740741</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>0.500046296296296</v>
       </c>
-      <c r="G13" s="0" t="str">
+      <c r="G13" s="1" t="str">
         <f aca="false">TEXT(F13-E13,"h:mm:ss")</f>
         <v>1:36:39</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="4" t="n">
         <f aca="false">HOUR(E13)+MINUTE(E13)/60+SECOND(E13)/3600</f>
         <v>10.3902777777778</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" s="4" t="n">
         <f aca="false">HOUR(F13)+MINUTE(F13)/60+SECOND(F13)/3600</f>
         <v>12.0011111111111</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="4" t="n">
         <f aca="false">SUM(I13-H13)</f>
         <v>1.61083333333333</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>26252</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="3" t="n">
         <v>0.436712962962963</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="3" t="n">
         <v>0.499363425925926</v>
       </c>
-      <c r="G14" s="0" t="str">
+      <c r="G14" s="1" t="str">
         <f aca="false">TEXT(F14-E14,"h:mm:ss")</f>
         <v>1:30:13</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="4" t="n">
         <f aca="false">HOUR(E14)+MINUTE(E14)/60+SECOND(E14)/3600</f>
         <v>10.4811111111111</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" s="4" t="n">
         <f aca="false">HOUR(F14)+MINUTE(F14)/60+SECOND(F14)/3600</f>
         <v>11.9847222222222</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="4" t="n">
         <f aca="false">SUM(I14-H14)</f>
         <v>1.50361111111111</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>26288</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="3" t="n">
         <v>0.613622685185185</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="5" t="n">
         <v>0.613622685185185</v>
       </c>
-      <c r="G15" s="0" t="str">
+      <c r="G15" s="1" t="str">
         <f aca="false">TEXT(F15-E15,"h:mm:ss")</f>
         <v>0:00:00</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="4" t="n">
         <f aca="false">HOUR(E15)+MINUTE(E15)/60+SECOND(E15)/3600</f>
         <v>14.7269444444444</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" s="4" t="n">
         <f aca="false">HOUR(F15)+MINUTE(F15)/60+SECOND(F15)/3600</f>
         <v>14.7269444444444</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="4" t="n">
         <f aca="false">SUM(I15-H15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>26228</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="3" t="n">
         <v>0.637372685185185</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="3" t="n">
         <v>0.661805555555556</v>
       </c>
-      <c r="G16" s="0" t="str">
+      <c r="G16" s="1" t="str">
         <f aca="false">TEXT(F16-E16,"h:mm:ss")</f>
         <v>0:35:11</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" s="4" t="n">
         <f aca="false">HOUR(E16)+MINUTE(E16)/60+SECOND(E16)/3600</f>
         <v>15.2969444444444</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" s="4" t="n">
         <f aca="false">HOUR(F16)+MINUTE(F16)/60+SECOND(F16)/3600</f>
         <v>15.8833333333333</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="4" t="n">
         <f aca="false">SUM(I16-H16)</f>
         <v>0.586388888888889</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B17" s="0" t="n">
+      <c r="A17" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B17" s="1" t="n">
         <v>26319</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="5" t="n">
         <v>0.460416666666667</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="5" t="n">
         <v>0.462534722222222</v>
       </c>
-      <c r="G17" s="0" t="str">
+      <c r="G17" s="1" t="str">
         <f aca="false">TEXT(F17-E17,"h:mm:ss")</f>
         <v>0:03:03</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="4" t="n">
         <f aca="false">HOUR(E17)+MINUTE(E17)/60+SECOND(E17)/3600</f>
         <v>11.05</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" s="4" t="n">
         <f aca="false">HOUR(F17)+MINUTE(F17)/60+SECOND(F17)/3600</f>
         <v>11.1008333333333</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="4" t="n">
         <f aca="false">SUM(I17-H17)</f>
         <v>0.0508333333333315</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B18" s="0" t="n">
+      <c r="A18" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B18" s="1" t="n">
         <v>26319</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="5" t="n">
         <v>0.472268518518519</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="5" t="n">
         <v>0.491134259259259</v>
       </c>
-      <c r="G18" s="0" t="str">
+      <c r="G18" s="1" t="str">
         <f aca="false">TEXT(F18-E18,"h:mm:ss")</f>
         <v>0:27:10</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" s="4" t="n">
         <f aca="false">HOUR(E18)+MINUTE(E18)/60+SECOND(E18)/3600</f>
         <v>11.3344444444444</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" s="4" t="n">
         <f aca="false">HOUR(F18)+MINUTE(F18)/60+SECOND(F18)/3600</f>
         <v>11.7872222222222</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="4" t="n">
         <f aca="false">SUM(I18-H18)</f>
         <v>0.452777777777778</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B19" s="0" t="n">
+      <c r="A19" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B19" s="1" t="n">
         <v>26323</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="5" t="n">
         <v>0.152256944444444</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="5" t="n">
         <v>0.174212962962963</v>
       </c>
-      <c r="G19" s="0" t="str">
+      <c r="G19" s="1" t="str">
         <f aca="false">TEXT(F19-E19,"h:mm:ss")</f>
         <v>0:31:37</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="4" t="n">
         <f aca="false">HOUR(E19)+MINUTE(E19)/60+SECOND(E19)/3600</f>
         <v>3.65416666666667</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" s="4" t="n">
         <f aca="false">HOUR(F19)+MINUTE(F19)/60+SECOND(F19)/3600</f>
         <v>4.18111111111111</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="4" t="n">
         <f aca="false">SUM(I19-H19)</f>
         <v>0.526944444444444</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B20" s="0" t="n">
+      <c r="A20" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B20" s="1" t="n">
         <v>26327</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="5" t="n">
         <v>0.55224537037037</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="5" t="n">
         <v>0.579456018518519</v>
       </c>
-      <c r="G20" s="0" t="str">
+      <c r="G20" s="1" t="str">
         <f aca="false">TEXT(F20-E20,"h:mm:ss")</f>
         <v>0:39:11</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" s="4" t="n">
         <f aca="false">HOUR(E20)+MINUTE(E20)/60+SECOND(E20)/3600</f>
         <v>13.2538888888889</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" s="4" t="n">
         <f aca="false">HOUR(F20)+MINUTE(F20)/60+SECOND(F20)/3600</f>
         <v>13.9069444444444</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="4" t="n">
         <f aca="false">SUM(I20-H20)</f>
         <v>0.653055555555556</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B21" s="0" t="n">
+      <c r="A21" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B21" s="1" t="n">
         <v>26327</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="5" t="n">
         <v>0.593344907407407</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="5" t="n">
         <v>0.706898148148148</v>
       </c>
-      <c r="G21" s="0" t="str">
+      <c r="G21" s="1" t="str">
         <f aca="false">TEXT(F21-E21,"h:mm:ss")</f>
         <v>2:43:31</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="4" t="n">
         <f aca="false">HOUR(E21)+MINUTE(E21)/60+SECOND(E21)/3600</f>
         <v>14.2402777777778</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" s="4" t="n">
         <f aca="false">HOUR(F21)+MINUTE(F21)/60+SECOND(F21)/3600</f>
         <v>16.9655555555556</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="4" t="n">
         <f aca="false">SUM(I21-H21)</f>
         <v>2.72527777777778</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B22" s="0" t="n">
+      <c r="A22" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B22" s="1" t="n">
         <v>26327</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="0" t="str">
+      <c r="G22" s="1" t="str">
         <f aca="false">TEXT(F22-E22,"h:mm:ss")</f>
         <v>0:00:00</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" s="4" t="n">
         <f aca="false">HOUR(E22)+MINUTE(E22)/60+SECOND(E22)/3600</f>
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" s="4" t="n">
         <f aca="false">HOUR(F22)+MINUTE(F22)/60+SECOND(F22)/3600</f>
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="4" t="n">
         <f aca="false">SUM(I22-H22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B23" s="0" t="n">
+      <c r="A23" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B23" s="1" t="n">
         <v>26331</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="5" t="n">
         <v>0.625243055555556</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="5" t="n">
         <v>0.688252314814815</v>
       </c>
-      <c r="G23" s="0" t="str">
+      <c r="G23" s="1" t="str">
         <f aca="false">TEXT(F23-E23,"h:mm:ss")</f>
         <v>1:30:44</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="4" t="n">
         <f aca="false">HOUR(E23)+MINUTE(E23)/60+SECOND(E23)/3600</f>
         <v>15.0058333333333</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" s="4" t="n">
         <f aca="false">HOUR(F23)+MINUTE(F23)/60+SECOND(F23)/3600</f>
         <v>16.5180555555556</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="4" t="n">
         <f aca="false">SUM(I23-H23)</f>
         <v>1.51222222222222</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B24" s="0" t="n">
+      <c r="A24" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B24" s="1" t="n">
         <v>26331</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="5" t="n">
         <v>0.349525462962963</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="5" t="n">
         <v>0.411458333333333</v>
       </c>
-      <c r="G24" s="0" t="str">
+      <c r="G24" s="1" t="str">
         <f aca="false">TEXT(F24-E24,"h:mm:ss")</f>
         <v>1:29:11</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="4" t="n">
         <f aca="false">HOUR(E24)+MINUTE(E24)/60+SECOND(E24)/3600</f>
         <v>8.38861111111111</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" s="4" t="n">
         <f aca="false">HOUR(F24)+MINUTE(F24)/60+SECOND(F24)/3600</f>
         <v>9.875</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="4" t="n">
         <f aca="false">SUM(I24-H24)</f>
         <v>1.48638888888889</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44259</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>26331</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="5" t="n">
         <v>0.470659722222222</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="5" t="n">
         <v>0.486585648148148</v>
       </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="K25" s="3"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="K25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44259</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>26331</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="5" t="n">
         <v>0.487777777777778</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="5" t="n">
         <v>0.491527777777778</v>
       </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="K26" s="3"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="K26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44259</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>26331</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="5" t="n">
         <v>0.548923611111111</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="5" t="n">
         <v>0.607673611111111</v>
       </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="K27" s="3"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="K27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B28" s="0" t="n">
+      <c r="A28" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B28" s="1" t="n">
         <v>26331</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G28" s="0" t="str">
+      <c r="G28" s="1" t="str">
         <f aca="false">TEXT(F28-E28,"h:mm:ss")</f>
         <v>0:00:00</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" s="4" t="n">
         <f aca="false">HOUR(E28)+MINUTE(E28)/60+SECOND(E28)/3600</f>
         <v>0</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" s="4" t="n">
         <f aca="false">HOUR(F28)+MINUTE(F28)/60+SECOND(F28)/3600</f>
         <v>0</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="4" t="n">
         <f aca="false">SUM(I28-H28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B29" s="0" t="n">
+      <c r="A29" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B29" s="1" t="n">
         <v>26333</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="5" t="n">
         <v>0.540520833333333</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="5" t="n">
         <v>0.554386574074074</v>
       </c>
-      <c r="G29" s="0" t="str">
+      <c r="G29" s="1" t="str">
         <f aca="false">TEXT(F29-E29,"h:mm:ss")</f>
         <v>0:19:58</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="4" t="n">
         <f aca="false">HOUR(E29)+MINUTE(E29)/60+SECOND(E29)/3600</f>
         <v>12.9725</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" s="4" t="n">
         <f aca="false">HOUR(F29)+MINUTE(F29)/60+SECOND(F29)/3600</f>
         <v>13.3052777777778</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="4" t="n">
         <f aca="false">SUM(I29-H29)</f>
         <v>0.332777777777778</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B30" s="0" t="n">
+      <c r="A30" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B30" s="1" t="n">
         <v>26333</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="5" t="n">
         <v>0.565983796296296</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="5" t="n">
         <v>0.598275462962963</v>
       </c>
-      <c r="G30" s="0" t="str">
+      <c r="G30" s="1" t="str">
         <f aca="false">TEXT(F30-E30,"h:mm:ss")</f>
         <v>0:46:30</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H30" s="4" t="n">
         <f aca="false">HOUR(E30)+MINUTE(E30)/60+SECOND(E30)/3600</f>
         <v>13.5836111111111</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" s="4" t="n">
         <f aca="false">HOUR(F30)+MINUTE(F30)/60+SECOND(F30)/3600</f>
         <v>14.3586111111111</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="4" t="n">
         <f aca="false">SUM(I30-H30)</f>
         <v>0.775</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44259</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>26340</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="5" t="n">
         <v>0.671377314814815</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="5" t="n">
         <v>0.710543981481482</v>
       </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="K31" s="3"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="K31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B32" s="0" t="n">
+      <c r="A32" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B32" s="1" t="n">
         <v>26340</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="5" t="n">
         <v>0.541122685185185</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="5" t="n">
         <v>0.541458333333333</v>
       </c>
-      <c r="G32" s="0" t="str">
+      <c r="G32" s="1" t="str">
         <f aca="false">TEXT(F32-E32,"h:mm:ss")</f>
         <v>0:00:29</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="H32" s="4" t="n">
         <f aca="false">HOUR(E32)+MINUTE(E32)/60+SECOND(E32)/3600</f>
         <v>12.9869444444444</v>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" s="4" t="n">
         <f aca="false">HOUR(F32)+MINUTE(F32)/60+SECOND(F32)/3600</f>
         <v>12.995</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="4" t="n">
         <f aca="false">SUM(I32-H32)</f>
         <v>0.00805555555555593</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44259</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>26340</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="5" t="n">
         <v>0.623391203703704</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="5" t="n">
         <v>0.669664351851852</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44260</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>26340</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="5" t="n">
         <v>0.332025462962963</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="5" t="n">
         <v>0.368402777777778</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B35" s="0" t="n">
+      <c r="A35" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B35" s="1" t="n">
         <v>26348</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B36" s="0" t="n">
+      <c r="A36" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B36" s="1" t="n">
         <v>26348</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B37" s="0" t="n">
+      <c r="A37" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B37" s="1" t="n">
         <v>26348</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B38" s="0" t="n">
+      <c r="A38" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B38" s="1" t="n">
         <v>26349</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B39" s="0" t="n">
+      <c r="A39" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B39" s="1" t="n">
         <v>26349</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B40" s="0" t="n">
+      <c r="A40" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B40" s="1" t="n">
         <v>26352</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B41" s="0" t="n">
+      <c r="A41" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B41" s="1" t="n">
         <v>26352</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B42" s="0" t="n">
+      <c r="A42" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B42" s="1" t="n">
         <v>26362</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="5" t="n">
         <v>0.674398148148148</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="5" t="n">
         <v>0.681041666666667</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B43" s="0" t="n">
+      <c r="A43" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B43" s="1" t="n">
         <v>26373</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="5" t="n">
         <v>0.672175925925926</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="5" t="n">
         <v>0.684039351851852</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B44" s="0" t="n">
+      <c r="A44" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B44" s="1" t="n">
         <v>26376</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B45" s="0" t="n">
+      <c r="A45" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B45" s="1" t="n">
         <v>26380</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B46" s="0" t="n">
+      <c r="A46" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B46" s="1" t="n">
         <v>26385</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="5" t="n">
         <v>0.355509259259259</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="5" t="n">
         <v>0.374236111111111</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B47" s="0" t="n">
+      <c r="A47" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="B47" s="1" t="n">
         <v>26385</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="5" t="n">
         <v>0.37787037037037</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1"/>
+      <c r="A48" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
